--- a/output/payroll_trend_report.xlsx
+++ b/output/payroll_trend_report.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -755,6 +755,50 @@
         <v>51</v>
       </c>
       <c r="L7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03-15T00:04:59.656040Z</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>147359.39</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11608.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24236.48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>47790.46</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1902.22</v>
+      </c>
+      <c r="J8" t="n">
+        <v>72</v>
+      </c>
+      <c r="K8" t="n">
+        <v>51</v>
+      </c>
+      <c r="L8" t="n">
         <v>50</v>
       </c>
     </row>
@@ -769,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +955,26 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>47790.46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-15T00:04:59.656040Z</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>47790.46</v>
       </c>
     </row>
@@ -925,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1211,36 @@
         <v>158968.09</v>
       </c>
       <c r="H7" t="n">
+        <v>30.06</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>147359.39</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11608.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>47790.46</v>
+      </c>
+      <c r="G8" t="n">
+        <v>158968.09</v>
+      </c>
+      <c r="H8" t="n">
         <v>30.06</v>
       </c>
     </row>
@@ -1161,7 +1255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1385,24 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>51</v>
+      </c>
+      <c r="D8" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1305,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1500,6 +1612,36 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>158968.09</v>
+      </c>
+      <c r="D7" t="n">
+        <v>158968.09</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>47790.46</v>
+      </c>
+      <c r="G7" t="n">
+        <v>47790.46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
